--- a/Results/lica_placebo_COEFFICIENT_SUMMARY.xlsx
+++ b/Results/lica_placebo_COEFFICIENT_SUMMARY.xlsx
@@ -486,42 +486,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.244</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-2.338, -0.149]</t>
+          <t>[-0.044, 0.331]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>1.154</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[0.096, 0.862]</t>
+          <t>[0.957, 1.392]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.026</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[-1.929, -0.123]</t>
+          <t>[-0.036, 0.273]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>1.126</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[0.145, 0.884]</t>
+          <t>[0.964, 1.314]</t>
         </is>
       </c>
     </row>
@@ -686,42 +686,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.150</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[0.000, 0.002]</t>
+          <t>[0.027, 0.273]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1.162</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[1.000, 1.002]</t>
+          <t>[1.027, 1.314]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[0.000, 0.001]</t>
+          <t>[0.022, 0.225]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1.132</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[1.000, 1.001]</t>
+          <t>[1.022, 1.253]</t>
         </is>
       </c>
     </row>

--- a/Results/lica_placebo_COEFFICIENT_SUMMARY.xlsx
+++ b/Results/lica_placebo_COEFFICIENT_SUMMARY.xlsx
@@ -486,42 +486,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>1.107</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.044, 0.331]</t>
+          <t>[0.193, 2.021]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>3.024</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[0.957, 1.392]</t>
+          <t>[1.213, 7.543]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.724</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[-0.036, 0.273]</t>
+          <t>[0.126, 1.321]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>2.062</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[0.964, 1.314]</t>
+          <t>[1.134, 3.748]</t>
         </is>
       </c>
     </row>
@@ -536,42 +536,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.121</t>
+          <t>-0.570</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.507, 0.266]</t>
+          <t>[-1.484, 0.345]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>0.566</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[0.602, 1.304]</t>
+          <t>[0.227, 1.411]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>-0.372</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[-0.418, 0.219]</t>
+          <t>[-0.970, 0.225]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>0.689</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[0.658, 1.245]</t>
+          <t>[0.379, 1.253]</t>
         </is>
       </c>
     </row>
@@ -586,42 +586,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[-0.359, 0.355]</t>
+          <t>[-0.727, 1.089]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>1.198</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[0.698, 1.426]</t>
+          <t>[0.483, 2.970]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[-0.297, 0.293]</t>
+          <t>[-0.476, 0.712]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[0.743, 1.340]</t>
+          <t>[0.621, 2.038]</t>
         </is>
       </c>
     </row>
@@ -636,42 +636,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.565</t>
+          <t>-1.048</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[-0.734, -0.395]</t>
+          <t>[-1.498, -0.597]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[0.480, 0.674]</t>
+          <t>[0.223, 0.551]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.466</t>
+          <t>-0.685</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[-0.606, -0.326]</t>
+          <t>[-0.980, -0.390]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>0.504</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[0.546, 0.722]</t>
+          <t>[0.375, 0.677]</t>
         </is>
       </c>
     </row>
@@ -681,47 +681,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Age_sq</t>
+          <t>Age_Sex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.150</t>
+          <t>-0.734</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[0.027, 0.273]</t>
+          <t>[-1.752, 0.284]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[1.027, 1.314]</t>
+          <t>[0.173, 1.328]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>-0.480</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[0.022, 0.225]</t>
+          <t>[-1.146, 0.186]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[1.022, 1.253]</t>
+          <t>[0.318, 1.204]</t>
         </is>
       </c>
     </row>
